--- a/quality-checks/lab-quality-checks/qualitychecks_summary.xlsx
+++ b/quality-checks/lab-quality-checks/qualitychecks_summary.xlsx
@@ -576,7 +576,7 @@
         <v>183</v>
       </c>
       <c r="D5" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="6">
@@ -587,10 +587,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +601,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D7" t="n">
         <v>53.2</v>
@@ -702,7 +702,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="15">
@@ -713,10 +713,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>84.9</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="17">
@@ -758,7 +758,7 @@
         <v>40</v>
       </c>
       <c r="D18" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="19">
@@ -769,10 +769,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D19" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="20">
@@ -825,10 +825,10 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="24">
@@ -839,10 +839,10 @@
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D24" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="25">
@@ -856,7 +856,7 @@
         <v>205</v>
       </c>
       <c r="D25" t="n">
-        <v>65.3</v>
+        <v>66.1</v>
       </c>
     </row>
     <row r="26">
@@ -993,10 +993,10 @@
         <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="36">
@@ -1007,10 +1007,10 @@
         <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D36" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="37">
@@ -1021,10 +1021,10 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D37" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="38">
@@ -1119,10 +1119,10 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1133,10 +1133,10 @@
         <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>15.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="46">
@@ -1147,10 +1147,10 @@
         <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D46" t="n">
-        <v>77.1</v>
+        <v>85.1</v>
       </c>
     </row>
     <row r="47">
@@ -1301,10 +1301,10 @@
         <v>6</v>
       </c>
       <c r="C57" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D57" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="58">
@@ -1318,7 +1318,7 @@
         <v>220</v>
       </c>
       <c r="D58" t="n">
-        <v>89.8</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="59">
@@ -1329,10 +1329,10 @@
         <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
@@ -1357,10 +1357,10 @@
         <v>7</v>
       </c>
       <c r="C61" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D61" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="62">
@@ -1458,7 +1458,7 @@
         <v>22</v>
       </c>
       <c r="D68" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="69">
@@ -1469,10 +1469,10 @@
         <v>6</v>
       </c>
       <c r="C69" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D69" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="70">
@@ -1483,10 +1483,10 @@
         <v>7</v>
       </c>
       <c r="C70" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D70" t="n">
-        <v>67</v>
+        <v>67.1</v>
       </c>
     </row>
     <row r="71">
@@ -1497,10 +1497,10 @@
         <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D71" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="72">
@@ -1511,10 +1511,10 @@
         <v>6</v>
       </c>
       <c r="C72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D72" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="73">
@@ -1528,7 +1528,7 @@
         <v>319</v>
       </c>
       <c r="D73" t="n">
-        <v>78.2</v>
+        <v>78.6</v>
       </c>
     </row>
     <row r="74">
@@ -1539,10 +1539,10 @@
         <v>5</v>
       </c>
       <c r="C74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D74" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="75">
@@ -1553,10 +1553,10 @@
         <v>6</v>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="76">
@@ -1567,10 +1567,10 @@
         <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D76" t="n">
-        <v>89.7</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="77">
@@ -1581,10 +1581,10 @@
         <v>5</v>
       </c>
       <c r="C77" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D77" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="78">
@@ -1595,10 +1595,10 @@
         <v>6</v>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="79">
@@ -1609,10 +1609,10 @@
         <v>7</v>
       </c>
       <c r="C79" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="D79" t="n">
-        <v>86.4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80">
@@ -1665,10 +1665,10 @@
         <v>6</v>
       </c>
       <c r="C83" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D83" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="84">
@@ -1682,7 +1682,7 @@
         <v>152</v>
       </c>
       <c r="D84" t="n">
-        <v>89.4</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="85">
@@ -1693,10 +1693,10 @@
         <v>5</v>
       </c>
       <c r="C85" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D85" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="86">
@@ -1707,10 +1707,10 @@
         <v>6</v>
       </c>
       <c r="C86" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D86" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="87">
@@ -1724,7 +1724,7 @@
         <v>135</v>
       </c>
       <c r="D87" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="88">
@@ -1864,7 +1864,7 @@
         <v>14</v>
       </c>
       <c r="D97" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="98">
@@ -1875,10 +1875,10 @@
         <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>18.3</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="99">
@@ -1892,7 +1892,7 @@
         <v>35</v>
       </c>
       <c r="D99" t="n">
-        <v>58.3</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="100">
@@ -1948,7 +1948,7 @@
         <v>89</v>
       </c>
       <c r="D103" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="104">
@@ -1959,10 +1959,10 @@
         <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D104" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="105">
@@ -1976,7 +1976,7 @@
         <v>239</v>
       </c>
       <c r="D105" t="n">
-        <v>67.7</v>
+        <v>67.9</v>
       </c>
     </row>
     <row r="106">
@@ -2071,10 +2071,10 @@
         <v>5</v>
       </c>
       <c r="C112" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D112" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="113">
@@ -2088,7 +2088,7 @@
         <v>45</v>
       </c>
       <c r="D113" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="114">
@@ -2102,7 +2102,7 @@
         <v>372</v>
       </c>
       <c r="D114" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115">
@@ -2180,7 +2180,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D2" t="n">
         <v>11.3</v>
@@ -2194,10 +2194,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D3" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4">
@@ -2208,10 +2208,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="D4" t="n">
-        <v>79.6</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="5">
@@ -2236,10 +2236,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D6" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -2250,10 +2250,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D7" t="n">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="8">
@@ -2264,10 +2264,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D8" t="n">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9">
@@ -2278,10 +2278,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="10">
@@ -2292,10 +2292,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="D10" t="n">
-        <v>84.4</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="11">
@@ -2306,10 +2306,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -2320,10 +2320,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>9.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="13">
@@ -2334,10 +2334,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D13" t="n">
-        <v>77.7</v>
+        <v>78.1</v>
       </c>
     </row>
     <row r="14">
@@ -2348,7 +2348,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" t="n">
         <v>9.7</v>
@@ -2362,10 +2362,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="16">
@@ -2376,10 +2376,10 @@
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D16" t="n">
-        <v>81.3</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="17">
@@ -2390,7 +2390,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D17" t="n">
         <v>9.9</v>
@@ -2404,10 +2404,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D18" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="19">
@@ -2418,10 +2418,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="D19" t="n">
-        <v>83.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -2432,10 +2432,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="21">
@@ -2460,10 +2460,10 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="D22" t="n">
-        <v>89.4</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="23">
@@ -2474,7 +2474,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D23" t="n">
         <v>19.5</v>
@@ -2488,10 +2488,10 @@
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D24" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="25">
@@ -2502,10 +2502,10 @@
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D25" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -2516,7 +2516,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D26" t="n">
         <v>8.9</v>
@@ -2530,10 +2530,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D27" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="28">
@@ -2547,7 +2547,7 @@
         <v>927</v>
       </c>
       <c r="D28" t="n">
-        <v>83.5</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
